--- a/consent_forms/018_medical_equipment_authorization_form--consent_forms.xlsx
+++ b/consent_forms/018_medical_equipment_authorization_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -800,8 +800,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,12 +829,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'cardiac'}</t>
+          <t>cardiac</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Cardiac'}</t>
+          <t>Cardiac</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'respiratory'}</t>
+          <t>respiratory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Respiratory'}</t>
+          <t>Respiratory</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'General'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'monitoring'}</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Monitoring'}</t>
+          <t>Monitoring</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_1_time_a_week'}</t>
+          <t>less_than_1_time_a_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 1 time a week'}</t>
+          <t>Less than 1 time a week</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_1_time_a_month'}</t>
+          <t>less_than_1_time_a_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 1 time a month'}</t>
+          <t>Less than 1 time a month</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'authorized_person_1'}</t>
+          <t>authorized_person_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Authorized Person 1'}</t>
+          <t>Authorized Person 1</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'authorized_person_2'}</t>
+          <t>authorized_person_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Authorized Person 2'}</t>
+          <t>Authorized Person 2</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'authorized_person_3'}</t>
+          <t>authorized_person_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Authorized Person 3'}</t>
+          <t>Authorized Person 3</t>
         </is>
       </c>
     </row>
